--- a/ValueSet-heartland-monitoring-track-vs.xlsx
+++ b/ValueSet-heartland-monitoring-track-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/ValueSet/heartland-monitoring-track-vs</t>
+    <t>https://fhir.heartlandprotocol.org/ValueSet/heartland-monitoring-track-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T15:03:58-04:00</t>
+    <t>2026-04-16T15:20:02-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://heartlandprotocol.org/fhir/CodeSystem/heartland-monitoring-track</t>
+    <t>https://fhir.heartlandprotocol.org/CodeSystem/heartland-monitoring-track</t>
   </si>
 </sst>
 </file>
